--- a/Excel File/NEW List Pengajuan Verifikasi MCU KPC.xlsx
+++ b/Excel File/NEW List Pengajuan Verifikasi MCU KPC.xlsx
@@ -1070,59 +1070,59 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>3</v>
+      <c r="A10" t="str">
+        <v/>
       </c>
       <c r="B10" t="str">
-        <v>diisi KPC</v>
+        <v/>
       </c>
       <c r="C10" t="str">
-        <v>04-Jul-26</v>
+        <v/>
       </c>
       <c r="D10" t="str">
-        <v>Trakindo</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>Z112354</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>YUSRONA FADLI MAHARDIKA</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>WAREHOUSEMAN</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>10-Aug-99</v>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <v>TIRTA MEDICAL CENTRE</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="L10" t="str">
-        <v>BP: 120/80</v>
+        <v/>
       </c>
       <c r="M10" t="str">
-        <v>TC: 153 TG: 73</v>
+        <v/>
       </c>
       <c r="N10" t="str">
-        <v>GF: 108.3</v>
+        <v/>
       </c>
       <c r="O10" t="str">
-        <v>BMI: 24.51</v>
+        <v/>
       </c>
       <c r="P10" t="str">
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>SGPT: 19 SGOT: 21</v>
+        <v/>
       </c>
       <c r="R10" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="S10" t="str">
         <v/>
@@ -1144,59 +1144,77 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>4</v>
+      <c r="A11" t="str">
+        <v/>
       </c>
       <c r="B11" t="str">
-        <v>diisi KPC</v>
+        <v/>
       </c>
       <c r="C11" t="str">
-        <v>07-Jul-26</v>
+        <v/>
       </c>
       <c r="D11" t="str">
-        <v>Trakindo</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>Z61166</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>FIRDAUS</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>WAREHOUSEMAN</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>13-Aug-89</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>TIRTA MEDICAL CENTRE</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="L11" t="str">
-        <v>BP: 110/70</v>
+        <v/>
       </c>
       <c r="M11" t="str">
-        <v>TC: 206 TG: 237</v>
+        <v/>
       </c>
       <c r="N11" t="str">
-        <v>GF: 108.3</v>
+        <v/>
       </c>
       <c r="O11" t="str">
-        <v>BMI: 25.28</v>
+        <v/>
       </c>
       <c r="P11" t="str">
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>SGPT: 30 SGOT: 21</v>
+        <v/>
       </c>
       <c r="R11" t="str">
-        <v>Yes</v>
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Excel File/NEW List Pengajuan Verifikasi MCU KPC.xlsx
+++ b/Excel File/NEW List Pengajuan Verifikasi MCU KPC.xlsx
@@ -922,59 +922,59 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>1</v>
+      <c r="A8" t="str">
+        <v/>
       </c>
       <c r="B8" t="str">
-        <v>diisi KPC</v>
+        <v/>
       </c>
       <c r="C8" t="str">
-        <v>07-Jul-26</v>
+        <v/>
       </c>
       <c r="D8" t="str">
-        <v>Trakindo</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>Z100948</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>EKO IDJAYANTO</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>TEKNISI</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>22-Sep-94</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>TIRTA MEDICAL CENTRE</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>BP: 110/78</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>TC: 219 TG: 182</v>
+        <v/>
       </c>
       <c r="N8" t="str">
-        <v>GF: 119.8</v>
+        <v/>
       </c>
       <c r="O8" t="str">
-        <v>BMI: 27.15</v>
+        <v/>
       </c>
       <c r="P8" t="str">
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v>SGPT: 40 SGOT: 11</v>
+        <v/>
       </c>
       <c r="R8" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="S8" t="str">
         <v/>
@@ -996,59 +996,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>2</v>
+      <c r="A9" t="str">
+        <v/>
       </c>
       <c r="B9" t="str">
-        <v>diisi KPC</v>
+        <v/>
       </c>
       <c r="C9" t="str">
-        <v>07-Jul-26</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>Trakindo</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>Z108869</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>INDRADI FAHMI ALANWARI</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>M</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>SAFETYMAN</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>09-Aug-98</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>TIRTA MEDICAL CENTRE</v>
+        <v/>
       </c>
       <c r="K9" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="L9" t="str">
-        <v>BP: 120/80</v>
+        <v/>
       </c>
       <c r="M9" t="str">
-        <v>TC: 230 TG: 75</v>
+        <v/>
       </c>
       <c r="N9" t="str">
-        <v>GF: 122.6</v>
+        <v/>
       </c>
       <c r="O9" t="str">
-        <v>BMI: 28.07</v>
+        <v/>
       </c>
       <c r="P9" t="str">
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v>SGPT: 33 SGOT: 22</v>
+        <v/>
       </c>
       <c r="R9" t="str">
-        <v>No</v>
+        <v/>
       </c>
       <c r="S9" t="str">
         <v/>
